--- a/RQs_implementation/RQ2/livecodebench_rating.xlsx
+++ b/RQs_implementation/RQ2/livecodebench_rating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,42 +466,22 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>harmonic_mean</t>
+          <t>score</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>hm_rank</t>
+          <t>regression_rank</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>am_mean</t>
+          <t>distance</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>am_rank</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
           <t>distance_rank</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>regression_rank</t>
         </is>
       </c>
     </row>
@@ -537,29 +517,17 @@
         <v>0.3150795049253524</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2653421324674153</v>
+        <v>0.6063422871574479</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2721230857960095</v>
+        <v>1.031164444863708</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.031164444863708</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.6063422871574479</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -596,25 +564,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4646803271914837</v>
+        <v>1.002491853906655</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.002491853906655</v>
-      </c>
-      <c r="N3" t="n">
         <v>2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -649,27 +605,15 @@
         <v>0.2313038475708429</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03822387591108407</v>
+        <v>0.04883975170654294</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1260685904520881</v>
+        <v>1.244853861250589</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.244853861250589</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.04883975170654294</v>
-      </c>
-      <c r="P4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -705,28 +649,16 @@
         <v>0.8199505008388774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.332248772821787</v>
+        <v>0.8963045307487884</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5141419170861053</v>
+        <v>0.8118829553939918</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.8118829553939918</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.8963045307487884</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -761,28 +693,16 @@
         <v>0.9564302284895483</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6744101145909104</v>
+        <v>2.594182248952598</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7386317809114408</v>
+        <v>0.4811434499542911</v>
       </c>
       <c r="L6" t="n">
         <v>4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.4811434499542911</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.594182248952598</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -817,28 +737,16 @@
         <v>0.7832440852444773</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5071755352926021</v>
+        <v>1.55634289071748</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5791220426222387</v>
+        <v>0.6615195587293723</v>
       </c>
       <c r="L7" t="n">
         <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.6615195587293723</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.55634289071748</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -873,28 +781,16 @@
         <v>0.9993437366586101</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6477495269183687</v>
+        <v>2.511138150787263</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7392552016626384</v>
+        <v>0.5208337467874796</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.5208337467874796</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.511138150787263</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -929,28 +825,16 @@
         <v>0.7836746869021529</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1838904654699964</v>
+        <v>0.4324967432237062</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4439206767844098</v>
+        <v>0.9215823360926536</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.9215823360926536</v>
-      </c>
-      <c r="N9" t="n">
         <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.4324967432237062</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -985,28 +869,16 @@
         <v>0.7696341147694327</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6636571105166778</v>
+        <v>2.389666518351428</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.676483724051383</v>
+        <v>0.4761087608826097</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.4761087608826097</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.389666518351428</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1041,27 +913,15 @@
         <v>0.1526582179122973</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06546520373302327</v>
+        <v>0.08499158637298228</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09716244228948198</v>
+        <v>1.279214944194033</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.279214944194033</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.08499158637298228</v>
-      </c>
-      <c r="P11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1097,28 +957,16 @@
         <v>0.8609519497605012</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04068223704167918</v>
+        <v>0.09345521806269619</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4408926415469173</v>
+        <v>0.9889902534335296</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.9889902534335296</v>
-      </c>
-      <c r="N12" t="n">
         <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.09345521806269619</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1153,28 +1001,16 @@
         <v>0.9931754500551946</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4256062477701976</v>
+        <v>1.408774396004642</v>
       </c>
       <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7291986027549195</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.6320043916942639</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.7291986027549195</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.408774396004642</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1209,27 +1045,15 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.4812018444456221</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1666666666666667</v>
+        <v>1.201850425154663</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.201850425154663</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.4812018444456221</v>
-      </c>
-      <c r="P14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1265,28 +1089,16 @@
         <v>0.7423497013387048</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3253580470850611</v>
+        <v>0.8318681087548455</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0.475341517336019</v>
+        <v>0.8325381597929106</v>
       </c>
       <c r="L15" t="n">
         <v>3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.8325381597929106</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.8318681087548455</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1321,28 +1133,16 @@
         <v>0.8475197675148197</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4566300243586108</v>
+        <v>1.382498737531991</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5800098837574099</v>
+        <v>0.7042062704199208</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.7042062704199208</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.382498737531991</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1377,28 +1177,16 @@
         <v>0.67733346733848</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1144401911444948</v>
+        <v>0.235302725942929</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0.36991673366924</v>
+        <v>0.9914736210811701</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.9914736210811701</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.235302725942929</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1433,28 +1221,16 @@
         <v>0.7332835738967957</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2432832015411487</v>
+        <v>0.5774492630931932</v>
       </c>
       <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.8948398439931642</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.4395584536150645</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.8948398439931642</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.5774492630931932</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1489,27 +1265,15 @@
         <v>0.8776686023858781</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9348493139531224</v>
+        <v>4.565296096887642</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.938834301192939</v>
+        <v>0.1223313976141219</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.1223313976141219</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4.565296096887642</v>
-      </c>
-      <c r="P19" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1545,28 +1309,16 @@
         <v>0.9925503962122996</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1175951404520131</v>
+        <v>0.3248567791267464</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5275251981061497</v>
+        <v>0.9375295977176368</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.9375295977176368</v>
-      </c>
-      <c r="N20" t="n">
         <v>2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.3248567791267464</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1601,28 +1353,16 @@
         <v>0.6098792904706269</v>
       </c>
       <c r="I21" t="n">
-        <v>0.495090101446752</v>
+        <v>1.479020355582178</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5132729785686467</v>
+        <v>0.701763454293168</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.701763454293168</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.479020355582178</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1657,28 +1397,16 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1886792452830188</v>
+        <v>0.5463355353315965</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.8958333333333334</v>
-      </c>
-      <c r="N22" t="n">
         <v>2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.5463355353315965</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1713,28 +1441,16 @@
         <v>0.6830686259389415</v>
       </c>
       <c r="I23" t="n">
-        <v>0.04043346146795833</v>
+        <v>0.07883405397813348</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3519509796361374</v>
+        <v>1.029180672659248</v>
       </c>
       <c r="L23" t="n">
         <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.029180672659248</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.07883405397813348</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/RQs_implementation/RQ2/livecodebench_rating.xlsx
+++ b/RQs_implementation/RQ2/livecodebench_rating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,42 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>harmonic_mean</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>hm_rank</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>am_mean</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>am_rank</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>distance_rank</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>regression_rank</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>distance</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>distance_rank</t>
         </is>
       </c>
     </row>
@@ -517,16 +537,28 @@
         <v>0.3150795049253524</v>
       </c>
       <c r="I2" t="n">
+        <v>0.2653421324674153</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2721230857960095</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.031164444863708</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
         <v>0.6063422871574479</v>
       </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.031164444863708</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -564,13 +596,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
+        <v>0.4646803271914837</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
         <v>1.002491853906655</v>
       </c>
-      <c r="L3" t="n">
-        <v>2</v>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -605,15 +649,27 @@
         <v>0.2313038475708429</v>
       </c>
       <c r="I4" t="n">
+        <v>0.03822387591108407</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.1260685904520881</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.244853861250589</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.04883975170654294</v>
       </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.244853861250589</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -649,16 +705,28 @@
         <v>0.8199505008388774</v>
       </c>
       <c r="I5" t="n">
+        <v>0.332248772821787</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5141419170861053</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8118829553939918</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
         <v>0.8963045307487884</v>
       </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.8118829553939918</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
+      <c r="P5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -693,16 +761,28 @@
         <v>0.9564302284895483</v>
       </c>
       <c r="I6" t="n">
-        <v>2.594182248952598</v>
+        <v>0.6744101145909104</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4811434499542911</v>
+        <v>0.7386317809114408</v>
       </c>
       <c r="L6" t="n">
         <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4811434499542911</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.594182248952598</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -737,16 +817,28 @@
         <v>0.7832440852444773</v>
       </c>
       <c r="I7" t="n">
+        <v>0.5071755352926021</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5791220426222387</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6615195587293723</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>1.55634289071748</v>
       </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.6615195587293723</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
+      <c r="P7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -781,16 +873,28 @@
         <v>0.9993437366586101</v>
       </c>
       <c r="I8" t="n">
-        <v>2.511138150787263</v>
+        <v>0.6477495269183687</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5208337467874796</v>
+        <v>0.7392552016626384</v>
       </c>
       <c r="L8" t="n">
         <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5208337467874796</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.511138150787263</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -825,16 +929,28 @@
         <v>0.7836746869021529</v>
       </c>
       <c r="I9" t="n">
+        <v>0.1838904654699964</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4439206767844098</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.9215823360926536</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.4324967432237062</v>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.9215823360926536</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
+      <c r="P9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -869,16 +985,28 @@
         <v>0.7696341147694327</v>
       </c>
       <c r="I10" t="n">
-        <v>2.389666518351428</v>
+        <v>0.6636571105166778</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4761087608826097</v>
+        <v>0.676483724051383</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4761087608826097</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.389666518351428</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -913,15 +1041,27 @@
         <v>0.1526582179122973</v>
       </c>
       <c r="I11" t="n">
+        <v>0.06546520373302327</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.09716244228948198</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.279214944194033</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.08499158637298228</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.279214944194033</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -957,16 +1097,28 @@
         <v>0.8609519497605012</v>
       </c>
       <c r="I12" t="n">
+        <v>0.04068223704167918</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4408926415469173</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.9889902534335296</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.09345521806269619</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.9889902534335296</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
+      <c r="P12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1001,16 +1153,28 @@
         <v>0.9931754500551946</v>
       </c>
       <c r="I13" t="n">
+        <v>0.4256062477701976</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6320043916942639</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.7291986027549195</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.408774396004642</v>
       </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.7291986027549195</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
+      <c r="P13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1045,15 +1209,27 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.201850425154663</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.4812018444456221</v>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.201850425154663</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1089,16 +1265,28 @@
         <v>0.7423497013387048</v>
       </c>
       <c r="I15" t="n">
+        <v>0.3253580470850611</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.475341517336019</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.8325381597929106</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.8318681087548455</v>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.8325381597929106</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3</v>
+      <c r="P15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1133,16 +1321,28 @@
         <v>0.8475197675148197</v>
       </c>
       <c r="I16" t="n">
+        <v>0.4566300243586108</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5800098837574099</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.7042062704199208</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.382498737531991</v>
       </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.7042062704199208</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3</v>
+      <c r="P16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1177,16 +1377,28 @@
         <v>0.67733346733848</v>
       </c>
       <c r="I17" t="n">
+        <v>0.1144401911444948</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.36991673366924</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.9914736210811701</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.235302725942929</v>
       </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.9914736210811701</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
+      <c r="P17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1221,16 +1433,28 @@
         <v>0.7332835738967957</v>
       </c>
       <c r="I18" t="n">
+        <v>0.2432832015411487</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.4395584536150645</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.8948398439931642</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
         <v>0.5774492630931932</v>
       </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.8948398439931642</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
+      <c r="P18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1265,15 +1489,27 @@
         <v>0.8776686023858781</v>
       </c>
       <c r="I19" t="n">
-        <v>4.565296096887642</v>
+        <v>0.9348493139531224</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
       </c>
       <c r="K19" t="n">
+        <v>0.938834301192939</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.1223313976141219</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.565296096887642</v>
+      </c>
+      <c r="P19" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1309,16 +1545,28 @@
         <v>0.9925503962122996</v>
       </c>
       <c r="I20" t="n">
+        <v>0.1175951404520131</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.5275251981061497</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.9375295977176368</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.3248567791267464</v>
       </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.9375295977176368</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
+      <c r="P20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1353,16 +1601,28 @@
         <v>0.6098792904706269</v>
       </c>
       <c r="I21" t="n">
+        <v>0.495090101446752</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.5132729785686467</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.701763454293168</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
         <v>1.479020355582178</v>
       </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.701763454293168</v>
-      </c>
-      <c r="L21" t="n">
-        <v>3</v>
+      <c r="P21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1397,16 +1657,28 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
+        <v>0.1886792452830188</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" t="n">
         <v>0.5463355353315965</v>
       </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.8958333333333334</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2</v>
+      <c r="P22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1441,16 +1713,28 @@
         <v>0.6830686259389415</v>
       </c>
       <c r="I23" t="n">
+        <v>0.04043346146795833</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.3519509796361374</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.029180672659248</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.07883405397813348</v>
       </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.029180672659248</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
+      <c r="P23" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
